--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487727_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487727_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6249</v>
+        <v>6.3695</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6271</v>
+        <v>2.2082</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9978</v>
+        <v>4.1613</v>
       </c>
       <c r="G2" t="n">
         <v>1.9868</v>
@@ -610,13 +610,13 @@
         <v>2.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5166</v>
+        <v>1.2612</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1787</v>
+        <v>0.7598</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3378</v>
+        <v>0.5014</v>
       </c>
       <c r="V2" t="n">
         <v>2.3454</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8871</v>
+        <v>3.3121</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2047</v>
+        <v>1.984</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6824</v>
+        <v>1.3281</v>
       </c>
       <c r="G3" t="n">
         <v>1.9909</v>
@@ -688,13 +688,13 @@
         <v>3.4926</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6763</v>
+        <v>2.1013</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7392</v>
+        <v>1.5186</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.5827</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1979</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2293</v>
+        <v>1.1419</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3857</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8436</v>
+        <v>1.8974</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5985</v>
+        <v>-0.0497</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5635</v>
+        <v>-2.2714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.035</v>
+        <v>2.2217</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0818</v>
+        <v>0.7645</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0412</v>
+        <v>-1.8743</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0406</v>
+        <v>2.6388</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5168</v>
+        <v>-0.8142</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5223</v>
+        <v>-0.3971</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0056</v>
+        <v>-0.4171</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3881</v>
+        <v>3.2985</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2427</v>
+        <v>0.3794</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3039</v>
+        <v>0.1382</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0612</v>
+        <v>0.2412</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.546</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7613</v>
+        <v>0.9586</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0256</v>
+        <v>0.3353</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7869</v>
+        <v>0.6234</v>
       </c>
       <c r="G5" t="n">
         <v>1.0912</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1086</v>
+        <v>0.3059</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1817</v>
+        <v>0.1792</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2903</v>
+        <v>0.1267</v>
       </c>
       <c r="V5" t="n">
         <v>0.7257</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5936</v>
+        <v>0.8834</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9768</v>
+        <v>-0.0147</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5704</v>
+        <v>0.8981</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0497</v>
+        <v>0.5985</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2714</v>
+        <v>0.5635</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2217</v>
+        <v>0.035</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7645</v>
+        <v>0.0818</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.8743</v>
+        <v>0.0412</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6388</v>
+        <v>0.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8142</v>
+        <v>0.5168</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3971</v>
+        <v>0.5223</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4171</v>
+        <v>-0.0056</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2985</v>
+        <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1689</v>
+        <v>-0.1032</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.083</v>
+        <v>-0.0965</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0859</v>
+        <v>-0.0067</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.546</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7805</v>
+        <v>-0.6594</v>
       </c>
       <c r="F7" t="n">
         <v>1.3344</v>
@@ -1000,10 +1000,10 @@
         <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0606</v>
+        <v>0.1817</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2423</v>
+        <v>-0.1211</v>
       </c>
       <c r="U7" t="n">
         <v>0.3028</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3139</v>
+        <v>0.2382</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3974</v>
+        <v>0.458</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0835</v>
+        <v>-0.2198</v>
       </c>
       <c r="G8" t="n">
         <v>0.5629</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.055</v>
+        <v>-0.1307</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3028</v>
+        <v>-0.2423</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2479</v>
+        <v>0.1116</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6336</v>
+        <v>-1.4546</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8106</v>
+        <v>-1.5498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.177</v>
+        <v>0.0953</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8319</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4796</v>
+        <v>-0.3006</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6662</v>
+        <v>-0.4055</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1867</v>
+        <v>0.1049</v>
       </c>
       <c r="V9" t="n">
         <v>0.066</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3274</v>
+        <v>-1.5371</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0538</v>
+        <v>-2.6208</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7264</v>
+        <v>1.0837</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.484</v>
+        <v>-1.7983</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.161</v>
+        <v>-0.3468</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.323</v>
+        <v>-1.4514</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0296</v>
+        <v>-0.0765</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0802</v>
+        <v>0.6797</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0507</v>
+        <v>-0.7562</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4544</v>
+        <v>-1.7217</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0808</v>
+        <v>-1.0266</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3737</v>
+        <v>-0.6952</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7463</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1344</v>
+        <v>-3.1045</v>
       </c>
       <c r="R10" t="n">
-        <v>3.8806</v>
+        <v>2.5224</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0437</v>
+        <v>0.0516</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1138</v>
+        <v>-0.004</v>
       </c>
       <c r="U10" t="n">
-        <v>1.07</v>
+        <v>0.0556</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.546</v>
+        <v>0.7917</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2239</v>
+        <v>0.5642</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7698</v>
+        <v>0.2275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.953</v>
+        <v>-1.5746</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6824</v>
+        <v>-2.8922</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7294</v>
+        <v>1.3176</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7983</v>
+        <v>-3.484</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3468</v>
+        <v>-2.161</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4514</v>
+        <v>-1.323</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0765</v>
+        <v>-2.0296</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6797</v>
+        <v>-2.0802</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7562</v>
+        <v>0.0507</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7217</v>
+        <v>-1.4544</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0266</v>
+        <v>-0.0808</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6952</v>
+        <v>-1.3737</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1045</v>
+        <v>-2.1344</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5224</v>
+        <v>3.8806</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3643</v>
+        <v>0.7091</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0655</v>
+        <v>0.0479</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2988</v>
+        <v>0.6612</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7917</v>
+        <v>-0.546</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5642</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2275</v>
+        <v>-1.7698</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7801</v>
+        <v>-3.8341</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0928</v>
+        <v>-3.3922</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6872</v>
+        <v>-0.4419</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0885</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9154</v>
+        <v>0.0306</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.0591</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2739</v>
+        <v>-0.0286</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6119</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.269900000000001</v>
+        <v>5.1783</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.807600000000001</v>
+        <v>-6.899100000000001</v>
       </c>
       <c r="F13" t="n">
         <v>12.0776</v>
@@ -1444,19 +1444,19 @@
         <v>8.112400000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.578899999999999</v>
+        <v>2.5789</v>
       </c>
       <c r="L13" t="n">
         <v>5.5336</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.446899999999999</v>
+        <v>-9.446900000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-3.2463</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.2009</v>
+        <v>-6.200899999999999</v>
       </c>
       <c r="P13" t="n">
         <v>2.220446049250313e-16</v>
@@ -1468,13 +1468,13 @@
         <v>20.3733</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5779</v>
+        <v>4.4863</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9249000000000003</v>
+        <v>1.8334</v>
       </c>
       <c r="U13" t="n">
-        <v>2.652700000000001</v>
+        <v>2.6528</v>
       </c>
       <c r="V13" t="n">
         <v>2.027</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9191</v>
+        <v>7.9463</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4722</v>
+        <v>5.0718</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4469</v>
+        <v>2.8745</v>
       </c>
       <c r="G14" t="n">
         <v>7.5323</v>
@@ -1546,13 +1546,13 @@
         <v>3.1045</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2122</v>
+        <v>0.2395</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4385</v>
+        <v>0.0381</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2263</v>
+        <v>0.2014</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9896</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.709</v>
+        <v>2.5675</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7994</v>
+        <v>-0.501</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5085</v>
+        <v>3.0685</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1192</v>
+        <v>1.9025</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3996</v>
+        <v>1.1312</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7196</v>
+        <v>0.7713</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8255</v>
+        <v>1.7215</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0948</v>
+        <v>1.0669</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7307</v>
+        <v>0.6546</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2937</v>
+        <v>0.181</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3048</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0111</v>
+        <v>0.1168</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>3.2985</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4242</v>
+        <v>-1.2096</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0617</v>
+        <v>-0.7986</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3625</v>
+        <v>-0.411</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9418</v>
+        <v>0.5164</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>0.5164</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2489</v>
+        <v>1.6334</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9014</v>
+        <v>-0.8995</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1503</v>
+        <v>2.5329</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9025</v>
+        <v>1.1192</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1312</v>
+        <v>0.3996</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7713</v>
+        <v>0.7196</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7215</v>
+        <v>0.8255</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0669</v>
+        <v>0.0948</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6546</v>
+        <v>0.7307</v>
       </c>
       <c r="M16" t="n">
-        <v>0.181</v>
+        <v>0.2937</v>
       </c>
       <c r="N16" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.3048</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1168</v>
+        <v>-0.0111</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3582</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2985</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.5283</v>
+        <v>0.3485</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.199</v>
+        <v>-0.0384</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3293</v>
+        <v>0.387</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5164</v>
+        <v>0.9418</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5164</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1597</v>
+        <v>-0.4228</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0399</v>
+        <v>-3.2401</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8802</v>
+        <v>2.8172</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4162</v>
@@ -1780,13 +1780,13 @@
         <v>3.1045</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1386</v>
+        <v>-0.1245</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2277</v>
+        <v>-0.4279</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3664</v>
+        <v>0.3034</v>
       </c>
       <c r="V17" t="n">
         <v>0.894</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0158</v>
+        <v>-0.7884</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9496</v>
+        <v>-0.7494</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0663</v>
+        <v>-0.039</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2579</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0182</v>
+        <v>0.2456</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.2002</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1056</v>
+        <v>-1.2057</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8739</v>
+        <v>-0.974</v>
       </c>
       <c r="F19" t="n">
         <v>-0.2317</v>
@@ -1936,10 +1936,10 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2187</v>
+        <v>0.1186</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0011</v>
+        <v>-0.099</v>
       </c>
       <c r="U19" t="n">
         <v>0.2176</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0243</v>
+        <v>-1.8335</v>
       </c>
       <c r="E20" t="n">
         <v>1.0671</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0914</v>
+        <v>-2.9006</v>
       </c>
       <c r="G20" t="n">
         <v>0.184</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1036</v>
+        <v>0.2944</v>
       </c>
       <c r="T20" t="n">
         <v>0.1222</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0186</v>
+        <v>0.1722</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1179</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. COULIBALY</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.203</v>
+        <v>-1.9631</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8932</v>
+        <v>-5.1619</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6902</v>
+        <v>3.1988</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7634</v>
+        <v>-0.6169</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9147</v>
+        <v>1.4368</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1512</v>
+        <v>-2.0537</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6336</v>
+        <v>-1.1318</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.796</v>
+        <v>0.7662</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1624</v>
+        <v>-1.898</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1298</v>
+        <v>0.5149</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1187</v>
+        <v>0.6706</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0111</v>
+        <v>-0.1557</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>2.7164</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.464</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2894</v>
+        <v>-0.4316</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3856</v>
+        <v>-0.0325</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>S. COULIBALY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5181</v>
+        <v>-2.4722</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.262</v>
+        <v>-2.9933</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7439</v>
+        <v>0.5211</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6169</v>
+        <v>-1.7634</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4368</v>
+        <v>-1.9147</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0537</v>
+        <v>0.1512</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1318</v>
+        <v>-1.6336</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7662</v>
+        <v>-1.796</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.898</v>
+        <v>0.1624</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5149</v>
+        <v>-0.1298</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6706</v>
+        <v>-0.1187</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1557</v>
+        <v>-0.0111</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7164</v>
+        <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0191</v>
+        <v>-0.173</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5317</v>
+        <v>-0.3895</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4874</v>
+        <v>0.2165</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2821</v>
+        <v>-1.506</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7604</v>
+        <v>-2.8052</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1383</v>
+        <v>-2.2588</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6221</v>
+        <v>-0.5464</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4396</v>
+        <v>-3.1865</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0275</v>
+        <v>-2.0959</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4121</v>
+        <v>-1.0905</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2298</v>
+        <v>-1.9228</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9021</v>
+        <v>-1.9278</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6724</v>
+        <v>0.005</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2099</v>
+        <v>-1.2637</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1254</v>
+        <v>-0.1681</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0844</v>
+        <v>-1.0956</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1267</v>
+        <v>-0.5605</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0617</v>
+        <v>-0.5897</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1884</v>
+        <v>0.0292</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.9418</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3602</v>
+        <v>-2.9244</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7593</v>
+        <v>-1.4386</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6009</v>
+        <v>-1.4859</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1865</v>
+        <v>-2.4396</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0959</v>
+        <v>-2.0275</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0905</v>
+        <v>-0.4121</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9228</v>
+        <v>-0.2298</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9278</v>
+        <v>-0.9021</v>
       </c>
       <c r="L24" t="n">
-        <v>0.005</v>
+        <v>0.6724</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2637</v>
+        <v>-2.2099</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1681</v>
+        <v>-1.1254</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0956</v>
+        <v>-1.0844</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1155</v>
+        <v>-0.2908</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0902</v>
+        <v>-0.2386</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0253</v>
+        <v>-0.0521</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9418</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.270099999999999</v>
+        <v>-2.2681</v>
       </c>
       <c r="E25" t="n">
         <v>-12.0777</v>
       </c>
       <c r="F25" t="n">
-        <v>7.8076</v>
+        <v>9.8094</v>
       </c>
       <c r="G25" t="n">
         <v>1.3347</v>
@@ -2374,16 +2374,16 @@
         <v>0.6673000000000004</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6673999999999989</v>
+        <v>0.667399999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>9.447099999999997</v>
+        <v>9.447099999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>3.246299999999998</v>
+        <v>3.246300000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>6.2009</v>
+        <v>6.200899999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-8.1126</v>
@@ -2398,19 +2398,19 @@
         <v>0.0002000000000001445</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.3735</v>
+        <v>-20.37349999999999</v>
       </c>
       <c r="R25" t="n">
         <v>20.3732</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.5779</v>
+        <v>-1.5758</v>
       </c>
       <c r="T25" t="n">
         <v>-2.6528</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9249999999999998</v>
+        <v>1.0771</v>
       </c>
       <c r="V25" t="n">
         <v>-2.027</v>
